--- a/templates/inspection-report-template.xlsx
+++ b/templates/inspection-report-template.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\共有ドライブ\03-01-営業\01_案件管理\99.その他\クレー射撃\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC83DC57-F917-4B98-8BDB-6838A49B32A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D006FAB-8892-4C59-A5C2-DF021B6506DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="1452" windowWidth="21756" windowHeight="12168" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="29010" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TRAPAB" sheetId="6" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">TRAPAB!$A$1:$R$46</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">TRAPAB!$A$1:$R$45</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>西暦</t>
     <rPh sb="0" eb="2">
@@ -315,19 +315,6 @@
       <t>テキヨウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>一般社団法人　日本クレー射撃協会</t>
-    <rPh sb="0" eb="2">
-      <t>イッパン</t>
-    </rPh>
-    <rPh sb="2" eb="16">
-      <t>ニック</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Ａ</t>
   </si>
 </sst>
 </file>
@@ -400,7 +387,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="33">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -686,15 +673,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -809,7 +787,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -852,7 +830,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -862,6 +840,12 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -870,6 +854,10 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -882,12 +870,61 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -895,159 +932,89 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1444,7 +1411,7 @@
   <sheetPr codeName="Sheet2">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:S59"/>
+  <dimension ref="A2:R59"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="4.625" style="1" customWidth="1"/>
@@ -1458,33 +1425,33 @@
     <col min="15" max="15" width="4.625" customWidth="1"/>
     <col min="16" max="17" width="2.75" customWidth="1"/>
     <col min="18" max="18" width="3.625" customWidth="1"/>
-    <col min="19" max="19" width="0" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="9" customWidth="1"/>
     <col min="21" max="35" width="3.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3"/>
       <c r="B2" s="4"/>
       <c r="C2" s="5"/>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="23"/>
-      <c r="M2" s="23"/>
-      <c r="N2" s="23"/>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="23"/>
-    </row>
-    <row r="3" spans="1:19" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41"/>
+      <c r="P2" s="41"/>
+      <c r="Q2" s="41"/>
+      <c r="R2" s="41"/>
+    </row>
+    <row r="3" spans="1:18" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1498,8 +1465,8 @@
       <c r="K3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
       <c r="N3" s="14" t="s">
         <v>3</v>
       </c>
@@ -1512,137 +1479,137 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="29" t="s">
+    <row r="4" spans="1:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="34" t="s">
+      <c r="B4" s="37"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="35"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="37" t="s">
+      <c r="G4" s="48"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="38"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="29" t="s">
+      <c r="J4" s="54"/>
+      <c r="K4" s="55"/>
+      <c r="L4" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="40"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="41"/>
-      <c r="P4" s="42"/>
-      <c r="Q4" s="42"/>
-      <c r="R4" s="43"/>
-    </row>
-    <row r="5" spans="1:19" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="44" t="s">
+      <c r="M4" s="36"/>
+      <c r="N4" s="37"/>
+      <c r="O4" s="58"/>
+      <c r="P4" s="59"/>
+      <c r="Q4" s="59"/>
+      <c r="R4" s="16"/>
+    </row>
+    <row r="5" spans="1:18" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="49"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="63"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="47"/>
       <c r="G5" s="50"/>
       <c r="H5" s="51"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="53"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="44" t="s">
+      <c r="I5" s="53"/>
+      <c r="J5" s="56"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="M5" s="55"/>
-      <c r="N5" s="45"/>
-      <c r="O5" s="56"/>
-      <c r="P5" s="57"/>
-      <c r="Q5" s="57"/>
-      <c r="R5" s="58"/>
-    </row>
-    <row r="6" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="44" t="s">
+      <c r="M5" s="65"/>
+      <c r="N5" s="61"/>
+      <c r="O5" s="18"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="17"/>
+    </row>
+    <row r="6" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="59"/>
-      <c r="F6" s="29" t="s">
+      <c r="B6" s="61"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="40"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="32"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="44" t="s">
+      <c r="G6" s="36"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="M6" s="55"/>
-      <c r="N6" s="45"/>
-      <c r="O6" s="56"/>
-      <c r="P6" s="57"/>
-      <c r="Q6" s="57"/>
-      <c r="R6" s="58"/>
-    </row>
-    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="44" t="s">
+      <c r="M6" s="65"/>
+      <c r="N6" s="61"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="17"/>
+    </row>
+    <row r="7" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="45"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="44" t="s">
+      <c r="B7" s="61"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="55"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="57"/>
-      <c r="K7" s="59"/>
-      <c r="L7" s="44" t="s">
+      <c r="G7" s="65"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="M7" s="55"/>
-      <c r="N7" s="45"/>
-      <c r="O7" s="56"/>
-      <c r="P7" s="57"/>
-      <c r="Q7" s="57"/>
-      <c r="R7" s="58"/>
-    </row>
-    <row r="8" spans="1:19" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="60" t="s">
+      <c r="M7" s="65"/>
+      <c r="N7" s="61"/>
+      <c r="O7" s="18"/>
+      <c r="P7" s="19"/>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="17"/>
+    </row>
+    <row r="8" spans="1:18" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="61"/>
-      <c r="C8" s="62"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="60" t="s">
+      <c r="B8" s="40"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="65"/>
-      <c r="H8" s="61"/>
-      <c r="I8" s="62"/>
-      <c r="J8" s="63"/>
-      <c r="K8" s="64"/>
-      <c r="L8" s="66" t="s">
+      <c r="G8" s="39"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="M8" s="67"/>
-      <c r="N8" s="67"/>
-      <c r="O8" s="68"/>
-      <c r="P8" s="62"/>
-      <c r="Q8" s="63"/>
-      <c r="R8" s="64"/>
-    </row>
-    <row r="9" spans="1:19" s="1" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="M8" s="28"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="26"/>
+    </row>
+    <row r="9" spans="1:18" s="1" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="13" t="s">
         <v>20</v>
       </c>
@@ -1688,13 +1655,13 @@
       <c r="O9" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="P9" s="25" t="s">
+      <c r="P9" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="Q9" s="26"/>
-      <c r="R9" s="27"/>
-    </row>
-    <row r="10" spans="1:19" ht="17.45" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="Q9" s="32"/>
+      <c r="R9" s="33"/>
+    </row>
+    <row r="10" spans="1:18" ht="17.45" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10">
         <v>1</v>
       </c>
@@ -1718,14 +1685,11 @@
         <f t="shared" ref="O10:O44" si="0">IF(AND(I10="",N10=""),"",IF(AND(I10="",ISNUMBER(N10)),N10,IF(AND(N10="",ISNUMBER(I10)),I10,IF(AND(ISNUMBER(I10),ISNUMBER(N10)),I10+N10,""))))</f>
         <v>0</v>
       </c>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="17"/>
-      <c r="R10" s="21"/>
-      <c r="S10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P10" s="18"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="20"/>
+    </row>
+    <row r="11" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="10">
         <v>2</v>
       </c>
@@ -1737,7 +1701,7 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="12">
-        <f t="shared" ref="I10:I44" si="1">SUM(E11:H11)</f>
+        <f t="shared" ref="I11:I44" si="1">SUM(E11:H11)</f>
         <v>0</v>
       </c>
       <c r="J11" s="2"/>
@@ -1749,14 +1713,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="17"/>
-      <c r="R11" s="21"/>
-      <c r="S11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P11" s="18"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="20"/>
+    </row>
+    <row r="12" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10">
         <v>3</v>
       </c>
@@ -1780,11 +1741,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P12" s="28"/>
-      <c r="Q12" s="17"/>
-      <c r="R12" s="21"/>
-    </row>
-    <row r="13" spans="1:19" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P12" s="34"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="20"/>
+    </row>
+    <row r="13" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10">
         <v>4</v>
       </c>
@@ -1808,11 +1769,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P13" s="28"/>
-      <c r="Q13" s="17"/>
-      <c r="R13" s="21"/>
-    </row>
-    <row r="14" spans="1:19" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P13" s="34"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="20"/>
+    </row>
+    <row r="14" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10">
         <v>5</v>
       </c>
@@ -1836,11 +1797,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="17"/>
-      <c r="R14" s="21"/>
-    </row>
-    <row r="15" spans="1:19" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P14" s="18"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="20"/>
+    </row>
+    <row r="15" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10">
         <v>6</v>
       </c>
@@ -1864,11 +1825,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="17"/>
-      <c r="R15" s="21"/>
-    </row>
-    <row r="16" spans="1:19" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P15" s="18"/>
+      <c r="Q15" s="19"/>
+      <c r="R15" s="20"/>
+    </row>
+    <row r="16" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10">
         <v>7</v>
       </c>
@@ -1892,9 +1853,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="17"/>
-      <c r="R16" s="21"/>
+      <c r="P16" s="18"/>
+      <c r="Q16" s="19"/>
+      <c r="R16" s="20"/>
     </row>
     <row r="17" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10">
@@ -1920,9 +1881,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P17" s="16"/>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="21"/>
+      <c r="P17" s="18"/>
+      <c r="Q17" s="19"/>
+      <c r="R17" s="20"/>
     </row>
     <row r="18" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10">
@@ -1948,9 +1909,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="17"/>
-      <c r="R18" s="21"/>
+      <c r="P18" s="18"/>
+      <c r="Q18" s="19"/>
+      <c r="R18" s="20"/>
     </row>
     <row r="19" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10">
@@ -1976,9 +1937,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="21"/>
+      <c r="P19" s="18"/>
+      <c r="Q19" s="19"/>
+      <c r="R19" s="20"/>
     </row>
     <row r="20" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10">
@@ -2004,9 +1965,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P20" s="16"/>
-      <c r="Q20" s="17"/>
-      <c r="R20" s="21"/>
+      <c r="P20" s="18"/>
+      <c r="Q20" s="19"/>
+      <c r="R20" s="20"/>
     </row>
     <row r="21" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="10">
@@ -2032,9 +1993,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P21" s="16"/>
-      <c r="Q21" s="17"/>
-      <c r="R21" s="21"/>
+      <c r="P21" s="18"/>
+      <c r="Q21" s="19"/>
+      <c r="R21" s="20"/>
     </row>
     <row r="22" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="10">
@@ -2060,9 +2021,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P22" s="16"/>
-      <c r="Q22" s="17"/>
-      <c r="R22" s="21"/>
+      <c r="P22" s="18"/>
+      <c r="Q22" s="19"/>
+      <c r="R22" s="20"/>
     </row>
     <row r="23" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="10">
@@ -2088,9 +2049,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P23" s="16"/>
-      <c r="Q23" s="17"/>
-      <c r="R23" s="21"/>
+      <c r="P23" s="18"/>
+      <c r="Q23" s="19"/>
+      <c r="R23" s="20"/>
     </row>
     <row r="24" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="10">
@@ -2116,9 +2077,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P24" s="16"/>
-      <c r="Q24" s="17"/>
-      <c r="R24" s="21"/>
+      <c r="P24" s="18"/>
+      <c r="Q24" s="19"/>
+      <c r="R24" s="20"/>
     </row>
     <row r="25" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10">
@@ -2147,9 +2108,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P25" s="16"/>
-      <c r="Q25" s="17"/>
-      <c r="R25" s="21"/>
+      <c r="P25" s="18"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="20"/>
     </row>
     <row r="26" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10">
@@ -2175,9 +2136,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P26" s="16"/>
-      <c r="Q26" s="17"/>
-      <c r="R26" s="21"/>
+      <c r="P26" s="18"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="20"/>
     </row>
     <row r="27" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="10">
@@ -2203,9 +2164,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P27" s="16"/>
-      <c r="Q27" s="17"/>
-      <c r="R27" s="21"/>
+      <c r="P27" s="18"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="20"/>
     </row>
     <row r="28" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10">
@@ -2231,9 +2192,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P28" s="16"/>
-      <c r="Q28" s="17"/>
-      <c r="R28" s="21"/>
+      <c r="P28" s="18"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="20"/>
     </row>
     <row r="29" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="10">
@@ -2259,9 +2220,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P29" s="16"/>
-      <c r="Q29" s="17"/>
-      <c r="R29" s="21"/>
+      <c r="P29" s="18"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="20"/>
     </row>
     <row r="30" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="10">
@@ -2287,9 +2248,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P30" s="16"/>
-      <c r="Q30" s="17"/>
-      <c r="R30" s="21"/>
+      <c r="P30" s="18"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="20"/>
     </row>
     <row r="31" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="10">
@@ -2315,9 +2276,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P31" s="16"/>
-      <c r="Q31" s="17"/>
-      <c r="R31" s="21"/>
+      <c r="P31" s="18"/>
+      <c r="Q31" s="19"/>
+      <c r="R31" s="20"/>
     </row>
     <row r="32" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10">
@@ -2343,9 +2304,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P32" s="16"/>
-      <c r="Q32" s="17"/>
-      <c r="R32" s="21"/>
+      <c r="P32" s="18"/>
+      <c r="Q32" s="19"/>
+      <c r="R32" s="20"/>
     </row>
     <row r="33" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10">
@@ -2371,9 +2332,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P33" s="16"/>
-      <c r="Q33" s="17"/>
-      <c r="R33" s="21"/>
+      <c r="P33" s="18"/>
+      <c r="Q33" s="19"/>
+      <c r="R33" s="20"/>
     </row>
     <row r="34" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="10">
@@ -2399,9 +2360,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P34" s="18"/>
-      <c r="Q34" s="19"/>
-      <c r="R34" s="20"/>
+      <c r="P34" s="21"/>
+      <c r="Q34" s="22"/>
+      <c r="R34" s="23"/>
     </row>
     <row r="35" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="10">
@@ -2427,9 +2388,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P35" s="18"/>
-      <c r="Q35" s="19"/>
-      <c r="R35" s="20"/>
+      <c r="P35" s="21"/>
+      <c r="Q35" s="22"/>
+      <c r="R35" s="23"/>
     </row>
     <row r="36" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="10">
@@ -2455,9 +2416,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P36" s="18"/>
-      <c r="Q36" s="19"/>
-      <c r="R36" s="20"/>
+      <c r="P36" s="21"/>
+      <c r="Q36" s="22"/>
+      <c r="R36" s="23"/>
     </row>
     <row r="37" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="10">
@@ -2483,9 +2444,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P37" s="18"/>
-      <c r="Q37" s="19"/>
-      <c r="R37" s="20"/>
+      <c r="P37" s="21"/>
+      <c r="Q37" s="22"/>
+      <c r="R37" s="23"/>
     </row>
     <row r="38" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10">
@@ -2511,9 +2472,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P38" s="18"/>
-      <c r="Q38" s="19"/>
-      <c r="R38" s="20"/>
+      <c r="P38" s="21"/>
+      <c r="Q38" s="22"/>
+      <c r="R38" s="23"/>
     </row>
     <row r="39" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="10">
@@ -2539,9 +2500,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P39" s="18"/>
-      <c r="Q39" s="19"/>
-      <c r="R39" s="20"/>
+      <c r="P39" s="21"/>
+      <c r="Q39" s="22"/>
+      <c r="R39" s="23"/>
     </row>
     <row r="40" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="10">
@@ -2567,9 +2528,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P40" s="18"/>
-      <c r="Q40" s="19"/>
-      <c r="R40" s="20"/>
+      <c r="P40" s="21"/>
+      <c r="Q40" s="22"/>
+      <c r="R40" s="23"/>
     </row>
     <row r="41" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="10">
@@ -2595,9 +2556,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P41" s="18"/>
-      <c r="Q41" s="19"/>
-      <c r="R41" s="20"/>
+      <c r="P41" s="21"/>
+      <c r="Q41" s="22"/>
+      <c r="R41" s="23"/>
     </row>
     <row r="42" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="10">
@@ -2623,9 +2584,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P42" s="18"/>
-      <c r="Q42" s="19"/>
-      <c r="R42" s="20"/>
+      <c r="P42" s="21"/>
+      <c r="Q42" s="22"/>
+      <c r="R42" s="23"/>
     </row>
     <row r="43" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="10">
@@ -2651,9 +2612,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P43" s="18"/>
-      <c r="Q43" s="19"/>
-      <c r="R43" s="20"/>
+      <c r="P43" s="21"/>
+      <c r="Q43" s="22"/>
+      <c r="R43" s="23"/>
     </row>
     <row r="44" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10">
@@ -2679,9 +2640,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P44" s="18"/>
-      <c r="Q44" s="19"/>
-      <c r="R44" s="20"/>
+      <c r="P44" s="21"/>
+      <c r="Q44" s="22"/>
+      <c r="R44" s="23"/>
     </row>
     <row r="45" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="10">
@@ -2707,31 +2668,24 @@
         <f t="shared" ref="O45" si="3">IF(AND(I45="",N45=""),"",IF(AND(I45="",ISNUMBER(N45)),N45,IF(AND(N45="",ISNUMBER(I45)),I45,IF(AND(ISNUMBER(I45),ISNUMBER(N45)),I45+N45,""))))</f>
         <v>0</v>
       </c>
-      <c r="P45" s="18"/>
-      <c r="Q45" s="19"/>
-      <c r="R45" s="20"/>
+      <c r="P45" s="21"/>
+      <c r="Q45" s="22"/>
+      <c r="R45" s="23"/>
     </row>
     <row r="46" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="B46" s="22"/>
-      <c r="C46" s="22"/>
-      <c r="D46" s="22"/>
-      <c r="E46" s="22"/>
-      <c r="F46" s="22"/>
-      <c r="G46" s="22"/>
-      <c r="H46" s="22"/>
-      <c r="I46" s="22"/>
-      <c r="J46" s="22"/>
-      <c r="K46" s="22"/>
-      <c r="L46" s="22"/>
-      <c r="M46" s="22"/>
-      <c r="N46" s="22"/>
-      <c r="O46" s="22"/>
-      <c r="P46" s="22"/>
-      <c r="Q46" s="22"/>
-      <c r="R46" s="22"/>
+      <c r="A46"/>
+      <c r="B46"/>
+      <c r="C46"/>
+      <c r="D46"/>
+      <c r="E46"/>
+      <c r="F46"/>
+      <c r="G46"/>
+      <c r="H46"/>
+      <c r="I46"/>
+      <c r="J46"/>
+      <c r="K46"/>
+      <c r="L46"/>
+      <c r="M46"/>
     </row>
     <row r="47" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="48" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -2750,29 +2704,38 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C21:H22">
     <sortCondition ref="C21"/>
   </sortState>
-  <mergeCells count="70">
-    <mergeCell ref="P28:R28"/>
-    <mergeCell ref="P29:R29"/>
-    <mergeCell ref="P30:R30"/>
-    <mergeCell ref="P31:R31"/>
-    <mergeCell ref="P37:R37"/>
-    <mergeCell ref="P32:R32"/>
-    <mergeCell ref="P33:R33"/>
-    <mergeCell ref="P34:R34"/>
-    <mergeCell ref="P35:R35"/>
-    <mergeCell ref="P36:R36"/>
-    <mergeCell ref="P23:R23"/>
-    <mergeCell ref="P24:R24"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="L8:O8"/>
-    <mergeCell ref="P27:R27"/>
-    <mergeCell ref="P19:R19"/>
-    <mergeCell ref="P20:R20"/>
-    <mergeCell ref="P21:R21"/>
-    <mergeCell ref="P22:R22"/>
-    <mergeCell ref="P16:R16"/>
-    <mergeCell ref="P17:R17"/>
-    <mergeCell ref="P18:R18"/>
+  <mergeCells count="69">
+    <mergeCell ref="P45:R45"/>
+    <mergeCell ref="P44:R44"/>
+    <mergeCell ref="P11:R11"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="P8:R8"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="O7:Q7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="D2:R2"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:K5"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="O4:Q4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="O5:Q5"/>
+    <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:E6"/>
     <mergeCell ref="P43:R43"/>
     <mergeCell ref="P9:R9"/>
@@ -2789,41 +2752,31 @@
     <mergeCell ref="P25:R25"/>
     <mergeCell ref="P26:R26"/>
     <mergeCell ref="F6:H6"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="D2:R2"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="J4:K5"/>
-    <mergeCell ref="L4:N4"/>
-    <mergeCell ref="O4:Q4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="O5:Q5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="P45:R45"/>
-    <mergeCell ref="P44:R44"/>
-    <mergeCell ref="P11:R11"/>
-    <mergeCell ref="A46:R46"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="O6:Q6"/>
-    <mergeCell ref="P8:R8"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="O7:Q7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="P23:R23"/>
+    <mergeCell ref="P24:R24"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="L8:O8"/>
+    <mergeCell ref="P27:R27"/>
+    <mergeCell ref="P19:R19"/>
+    <mergeCell ref="P20:R20"/>
+    <mergeCell ref="P21:R21"/>
+    <mergeCell ref="P22:R22"/>
+    <mergeCell ref="P16:R16"/>
+    <mergeCell ref="P17:R17"/>
+    <mergeCell ref="P18:R18"/>
+    <mergeCell ref="P28:R28"/>
+    <mergeCell ref="P29:R29"/>
+    <mergeCell ref="P30:R30"/>
+    <mergeCell ref="P31:R31"/>
+    <mergeCell ref="P37:R37"/>
+    <mergeCell ref="P32:R32"/>
+    <mergeCell ref="P33:R33"/>
+    <mergeCell ref="P34:R34"/>
+    <mergeCell ref="P35:R35"/>
+    <mergeCell ref="P36:R36"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <dataValidations count="2">
+  <dataValidations disablePrompts="1" count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J4:K5" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"A,B,C"</formula1>
     </dataValidation>
@@ -2832,9 +2785,10 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="97" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;R&amp;"-,太字"&amp;12⑫</oddHeader>
+    <oddFooter>&amp;C一般社団法人　日本クレー射撃協会</oddFooter>
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>

--- a/templates/inspection-report-template.xlsx
+++ b/templates/inspection-report-template.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\共有ドライブ\03-01-営業\01_案件管理\99.その他\クレー射撃\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D006FAB-8892-4C59-A5C2-DF021B6506DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8213EFE1-87B3-4336-B23A-3FB87B0E4614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="29010" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TRAPAB" sheetId="6" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">TRAPAB!$A$1:$R$45</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -846,6 +843,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -858,18 +867,27 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -882,48 +900,17 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -932,17 +919,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -988,6 +969,9 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -995,12 +979,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1014,7 +992,26 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1411,7 +1408,7 @@
   <sheetPr codeName="Sheet2">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:R59"/>
+  <dimension ref="A2:R81"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="4.625" style="1" customWidth="1"/>
@@ -1433,23 +1430,23 @@
       <c r="A2" s="3"/>
       <c r="B2" s="4"/>
       <c r="C2" s="5"/>
-      <c r="D2" s="41" t="s">
+      <c r="D2" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="41"/>
-      <c r="R2" s="41"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="37"/>
+      <c r="N2" s="37"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="37"/>
+      <c r="R2" s="37"/>
     </row>
     <row r="3" spans="1:18" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3"/>
@@ -1465,8 +1462,8 @@
       <c r="K3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="42"/>
-      <c r="M3" s="42"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38"/>
       <c r="N3" s="14" t="s">
         <v>3</v>
       </c>
@@ -1480,134 +1477,134 @@
       </c>
     </row>
     <row r="4" spans="1:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="46" t="s">
+      <c r="B4" s="40"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="48"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="52" t="s">
+      <c r="G4" s="43"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="54"/>
-      <c r="K4" s="55"/>
-      <c r="L4" s="35" t="s">
+      <c r="J4" s="49"/>
+      <c r="K4" s="50"/>
+      <c r="L4" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="36"/>
-      <c r="N4" s="37"/>
-      <c r="O4" s="58"/>
-      <c r="P4" s="59"/>
-      <c r="Q4" s="59"/>
+      <c r="M4" s="53"/>
+      <c r="N4" s="40"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="55"/>
+      <c r="Q4" s="55"/>
       <c r="R4" s="16"/>
     </row>
     <row r="5" spans="1:18" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="60" t="s">
+      <c r="A5" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="61"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="56"/>
-      <c r="K5" s="57"/>
-      <c r="L5" s="60" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="51"/>
+      <c r="K5" s="52"/>
+      <c r="L5" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="M5" s="65"/>
-      <c r="N5" s="61"/>
-      <c r="O5" s="18"/>
-      <c r="P5" s="19"/>
-      <c r="Q5" s="19"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="29"/>
+      <c r="O5" s="21"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22"/>
       <c r="R5" s="17"/>
     </row>
     <row r="6" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="60" t="s">
+      <c r="A6" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="35" t="s">
+      <c r="B6" s="29"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="36"/>
-      <c r="H6" s="37"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="60" t="s">
+      <c r="G6" s="53"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="M6" s="65"/>
-      <c r="N6" s="61"/>
-      <c r="O6" s="18"/>
-      <c r="P6" s="19"/>
-      <c r="Q6" s="19"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="21"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22"/>
       <c r="R6" s="17"/>
     </row>
     <row r="7" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="60" t="s">
+      <c r="A7" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="61"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="60" t="s">
+      <c r="B7" s="29"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="65"/>
-      <c r="H7" s="61"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="60" t="s">
+      <c r="G7" s="28"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="33"/>
+      <c r="L7" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="M7" s="65"/>
-      <c r="N7" s="61"/>
-      <c r="O7" s="18"/>
-      <c r="P7" s="19"/>
-      <c r="Q7" s="19"/>
+      <c r="M7" s="28"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22"/>
       <c r="R7" s="17"/>
     </row>
     <row r="8" spans="1:18" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="40"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="38" t="s">
+      <c r="B8" s="35"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="39"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="24"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="27" t="s">
+      <c r="G8" s="36"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="M8" s="28"/>
-      <c r="N8" s="28"/>
-      <c r="O8" s="29"/>
-      <c r="P8" s="24"/>
-      <c r="Q8" s="25"/>
-      <c r="R8" s="26"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="64"/>
+      <c r="O8" s="65"/>
+      <c r="P8" s="30"/>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="32"/>
     </row>
     <row r="9" spans="1:18" s="1" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="13" t="s">
@@ -1655,13 +1652,13 @@
       <c r="O9" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="P9" s="31" t="s">
+      <c r="P9" s="59" t="s">
         <v>26</v>
       </c>
-      <c r="Q9" s="32"/>
-      <c r="R9" s="33"/>
-    </row>
-    <row r="10" spans="1:18" ht="17.45" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="Q9" s="60"/>
+      <c r="R9" s="61"/>
+    </row>
+    <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10">
         <v>1</v>
       </c>
@@ -1685,11 +1682,11 @@
         <f t="shared" ref="O10:O44" si="0">IF(AND(I10="",N10=""),"",IF(AND(I10="",ISNUMBER(N10)),N10,IF(AND(N10="",ISNUMBER(I10)),I10,IF(AND(ISNUMBER(I10),ISNUMBER(N10)),I10+N10,""))))</f>
         <v>0</v>
       </c>
-      <c r="P10" s="18"/>
-      <c r="Q10" s="19"/>
-      <c r="R10" s="20"/>
-    </row>
-    <row r="11" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P10" s="21"/>
+      <c r="Q10" s="22"/>
+      <c r="R10" s="23"/>
+    </row>
+    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="10">
         <v>2</v>
       </c>
@@ -1713,11 +1710,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P11" s="18"/>
-      <c r="Q11" s="19"/>
-      <c r="R11" s="20"/>
-    </row>
-    <row r="12" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P11" s="21"/>
+      <c r="Q11" s="22"/>
+      <c r="R11" s="23"/>
+    </row>
+    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10">
         <v>3</v>
       </c>
@@ -1741,11 +1738,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P12" s="34"/>
-      <c r="Q12" s="19"/>
-      <c r="R12" s="20"/>
-    </row>
-    <row r="13" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P12" s="62"/>
+      <c r="Q12" s="22"/>
+      <c r="R12" s="23"/>
+    </row>
+    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10">
         <v>4</v>
       </c>
@@ -1769,11 +1766,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P13" s="34"/>
-      <c r="Q13" s="19"/>
-      <c r="R13" s="20"/>
-    </row>
-    <row r="14" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P13" s="62"/>
+      <c r="Q13" s="22"/>
+      <c r="R13" s="23"/>
+    </row>
+    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10">
         <v>5</v>
       </c>
@@ -1797,11 +1794,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P14" s="18"/>
-      <c r="Q14" s="19"/>
-      <c r="R14" s="20"/>
-    </row>
-    <row r="15" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P14" s="21"/>
+      <c r="Q14" s="22"/>
+      <c r="R14" s="23"/>
+    </row>
+    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10">
         <v>6</v>
       </c>
@@ -1825,11 +1822,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P15" s="18"/>
-      <c r="Q15" s="19"/>
-      <c r="R15" s="20"/>
-    </row>
-    <row r="16" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P15" s="21"/>
+      <c r="Q15" s="22"/>
+      <c r="R15" s="23"/>
+    </row>
+    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10">
         <v>7</v>
       </c>
@@ -1853,11 +1850,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P16" s="18"/>
-      <c r="Q16" s="19"/>
-      <c r="R16" s="20"/>
-    </row>
-    <row r="17" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P16" s="21"/>
+      <c r="Q16" s="22"/>
+      <c r="R16" s="23"/>
+    </row>
+    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10">
         <v>8</v>
       </c>
@@ -1881,11 +1878,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P17" s="18"/>
-      <c r="Q17" s="19"/>
-      <c r="R17" s="20"/>
-    </row>
-    <row r="18" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P17" s="21"/>
+      <c r="Q17" s="22"/>
+      <c r="R17" s="23"/>
+    </row>
+    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10">
         <v>9</v>
       </c>
@@ -1909,11 +1906,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P18" s="18"/>
-      <c r="Q18" s="19"/>
-      <c r="R18" s="20"/>
-    </row>
-    <row r="19" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P18" s="21"/>
+      <c r="Q18" s="22"/>
+      <c r="R18" s="23"/>
+    </row>
+    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10">
         <v>10</v>
       </c>
@@ -1937,11 +1934,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P19" s="18"/>
-      <c r="Q19" s="19"/>
-      <c r="R19" s="20"/>
-    </row>
-    <row r="20" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P19" s="21"/>
+      <c r="Q19" s="22"/>
+      <c r="R19" s="23"/>
+    </row>
+    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10">
         <v>11</v>
       </c>
@@ -1965,11 +1962,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P20" s="18"/>
-      <c r="Q20" s="19"/>
-      <c r="R20" s="20"/>
-    </row>
-    <row r="21" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P20" s="21"/>
+      <c r="Q20" s="22"/>
+      <c r="R20" s="23"/>
+    </row>
+    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="10">
         <v>12</v>
       </c>
@@ -1993,11 +1990,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P21" s="18"/>
-      <c r="Q21" s="19"/>
-      <c r="R21" s="20"/>
-    </row>
-    <row r="22" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P21" s="21"/>
+      <c r="Q21" s="22"/>
+      <c r="R21" s="23"/>
+    </row>
+    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="10">
         <v>13</v>
       </c>
@@ -2021,11 +2018,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P22" s="18"/>
-      <c r="Q22" s="19"/>
-      <c r="R22" s="20"/>
-    </row>
-    <row r="23" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P22" s="21"/>
+      <c r="Q22" s="22"/>
+      <c r="R22" s="23"/>
+    </row>
+    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="10">
         <v>14</v>
       </c>
@@ -2049,11 +2046,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P23" s="18"/>
-      <c r="Q23" s="19"/>
-      <c r="R23" s="20"/>
-    </row>
-    <row r="24" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P23" s="21"/>
+      <c r="Q23" s="22"/>
+      <c r="R23" s="23"/>
+    </row>
+    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="10">
         <v>15</v>
       </c>
@@ -2077,11 +2074,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P24" s="18"/>
-      <c r="Q24" s="19"/>
-      <c r="R24" s="20"/>
-    </row>
-    <row r="25" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P24" s="21"/>
+      <c r="Q24" s="22"/>
+      <c r="R24" s="23"/>
+    </row>
+    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10">
         <v>16</v>
       </c>
@@ -2108,11 +2105,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P25" s="18"/>
-      <c r="Q25" s="19"/>
-      <c r="R25" s="20"/>
-    </row>
-    <row r="26" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P25" s="21"/>
+      <c r="Q25" s="22"/>
+      <c r="R25" s="23"/>
+    </row>
+    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10">
         <v>17</v>
       </c>
@@ -2136,11 +2133,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P26" s="18"/>
-      <c r="Q26" s="19"/>
-      <c r="R26" s="20"/>
-    </row>
-    <row r="27" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P26" s="21"/>
+      <c r="Q26" s="22"/>
+      <c r="R26" s="23"/>
+    </row>
+    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="10">
         <v>18</v>
       </c>
@@ -2164,11 +2161,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P27" s="18"/>
-      <c r="Q27" s="19"/>
-      <c r="R27" s="20"/>
-    </row>
-    <row r="28" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P27" s="21"/>
+      <c r="Q27" s="22"/>
+      <c r="R27" s="23"/>
+    </row>
+    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10">
         <v>19</v>
       </c>
@@ -2192,11 +2189,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P28" s="18"/>
-      <c r="Q28" s="19"/>
-      <c r="R28" s="20"/>
-    </row>
-    <row r="29" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P28" s="21"/>
+      <c r="Q28" s="22"/>
+      <c r="R28" s="23"/>
+    </row>
+    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="10">
         <v>20</v>
       </c>
@@ -2220,11 +2217,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P29" s="18"/>
-      <c r="Q29" s="19"/>
-      <c r="R29" s="20"/>
-    </row>
-    <row r="30" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P29" s="21"/>
+      <c r="Q29" s="22"/>
+      <c r="R29" s="23"/>
+    </row>
+    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="10">
         <v>21</v>
       </c>
@@ -2248,11 +2245,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P30" s="18"/>
-      <c r="Q30" s="19"/>
-      <c r="R30" s="20"/>
-    </row>
-    <row r="31" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P30" s="21"/>
+      <c r="Q30" s="22"/>
+      <c r="R30" s="23"/>
+    </row>
+    <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="10">
         <v>22</v>
       </c>
@@ -2276,11 +2273,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P31" s="18"/>
-      <c r="Q31" s="19"/>
-      <c r="R31" s="20"/>
-    </row>
-    <row r="32" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P31" s="21"/>
+      <c r="Q31" s="22"/>
+      <c r="R31" s="23"/>
+    </row>
+    <row r="32" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10">
         <v>23</v>
       </c>
@@ -2304,11 +2301,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P32" s="18"/>
-      <c r="Q32" s="19"/>
-      <c r="R32" s="20"/>
-    </row>
-    <row r="33" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P32" s="21"/>
+      <c r="Q32" s="22"/>
+      <c r="R32" s="23"/>
+    </row>
+    <row r="33" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10">
         <v>24</v>
       </c>
@@ -2332,11 +2329,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P33" s="18"/>
-      <c r="Q33" s="19"/>
-      <c r="R33" s="20"/>
-    </row>
-    <row r="34" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P33" s="21"/>
+      <c r="Q33" s="22"/>
+      <c r="R33" s="23"/>
+    </row>
+    <row r="34" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="10">
         <v>25</v>
       </c>
@@ -2360,11 +2357,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P34" s="21"/>
-      <c r="Q34" s="22"/>
-      <c r="R34" s="23"/>
-    </row>
-    <row r="35" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P34" s="18"/>
+      <c r="Q34" s="19"/>
+      <c r="R34" s="20"/>
+    </row>
+    <row r="35" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="10">
         <v>26</v>
       </c>
@@ -2388,11 +2385,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P35" s="21"/>
-      <c r="Q35" s="22"/>
-      <c r="R35" s="23"/>
-    </row>
-    <row r="36" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P35" s="18"/>
+      <c r="Q35" s="19"/>
+      <c r="R35" s="20"/>
+    </row>
+    <row r="36" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="10">
         <v>27</v>
       </c>
@@ -2416,11 +2413,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P36" s="21"/>
-      <c r="Q36" s="22"/>
-      <c r="R36" s="23"/>
-    </row>
-    <row r="37" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P36" s="18"/>
+      <c r="Q36" s="19"/>
+      <c r="R36" s="20"/>
+    </row>
+    <row r="37" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="10">
         <v>28</v>
       </c>
@@ -2444,11 +2441,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P37" s="21"/>
-      <c r="Q37" s="22"/>
-      <c r="R37" s="23"/>
-    </row>
-    <row r="38" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P37" s="18"/>
+      <c r="Q37" s="19"/>
+      <c r="R37" s="20"/>
+    </row>
+    <row r="38" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10">
         <v>29</v>
       </c>
@@ -2472,11 +2469,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P38" s="21"/>
-      <c r="Q38" s="22"/>
-      <c r="R38" s="23"/>
-    </row>
-    <row r="39" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P38" s="18"/>
+      <c r="Q38" s="19"/>
+      <c r="R38" s="20"/>
+    </row>
+    <row r="39" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="10">
         <v>30</v>
       </c>
@@ -2500,11 +2497,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P39" s="21"/>
-      <c r="Q39" s="22"/>
-      <c r="R39" s="23"/>
-    </row>
-    <row r="40" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P39" s="18"/>
+      <c r="Q39" s="19"/>
+      <c r="R39" s="20"/>
+    </row>
+    <row r="40" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="10">
         <v>31</v>
       </c>
@@ -2528,11 +2525,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P40" s="21"/>
-      <c r="Q40" s="22"/>
-      <c r="R40" s="23"/>
-    </row>
-    <row r="41" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P40" s="18"/>
+      <c r="Q40" s="19"/>
+      <c r="R40" s="20"/>
+    </row>
+    <row r="41" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="10">
         <v>32</v>
       </c>
@@ -2556,11 +2553,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P41" s="21"/>
-      <c r="Q41" s="22"/>
-      <c r="R41" s="23"/>
-    </row>
-    <row r="42" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P41" s="18"/>
+      <c r="Q41" s="19"/>
+      <c r="R41" s="20"/>
+    </row>
+    <row r="42" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="10">
         <v>33</v>
       </c>
@@ -2584,11 +2581,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P42" s="21"/>
-      <c r="Q42" s="22"/>
-      <c r="R42" s="23"/>
-    </row>
-    <row r="43" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P42" s="18"/>
+      <c r="Q42" s="19"/>
+      <c r="R42" s="20"/>
+    </row>
+    <row r="43" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="10">
         <v>34</v>
       </c>
@@ -2612,11 +2609,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P43" s="21"/>
-      <c r="Q43" s="22"/>
-      <c r="R43" s="23"/>
-    </row>
-    <row r="44" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P43" s="18"/>
+      <c r="Q43" s="19"/>
+      <c r="R43" s="20"/>
+    </row>
+    <row r="44" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10">
         <v>35</v>
       </c>
@@ -2640,11 +2637,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P44" s="21"/>
-      <c r="Q44" s="22"/>
-      <c r="R44" s="23"/>
-    </row>
-    <row r="45" spans="1:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P44" s="18"/>
+      <c r="Q44" s="19"/>
+      <c r="R44" s="20"/>
+    </row>
+    <row r="45" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="10">
         <v>36</v>
       </c>
@@ -2656,7 +2653,7 @@
       <c r="G45" s="11"/>
       <c r="H45" s="11"/>
       <c r="I45" s="12">
-        <f t="shared" ref="I45" si="2">SUM(E45:H45)</f>
+        <f t="shared" ref="I45:I46" si="2">SUM(E45:H45)</f>
         <v>0</v>
       </c>
       <c r="J45" s="11"/>
@@ -2665,59 +2662,1094 @@
       <c r="M45" s="11"/>
       <c r="N45" s="10"/>
       <c r="O45" s="12">
-        <f t="shared" ref="O45" si="3">IF(AND(I45="",N45=""),"",IF(AND(I45="",ISNUMBER(N45)),N45,IF(AND(N45="",ISNUMBER(I45)),I45,IF(AND(ISNUMBER(I45),ISNUMBER(N45)),I45+N45,""))))</f>
-        <v>0</v>
-      </c>
-      <c r="P45" s="21"/>
-      <c r="Q45" s="22"/>
-      <c r="R45" s="23"/>
-    </row>
-    <row r="46" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46"/>
-      <c r="B46"/>
-      <c r="C46"/>
-      <c r="D46"/>
-      <c r="E46"/>
-      <c r="F46"/>
-      <c r="G46"/>
-      <c r="H46"/>
-      <c r="I46"/>
-      <c r="J46"/>
-      <c r="K46"/>
-      <c r="L46"/>
-      <c r="M46"/>
-    </row>
-    <row r="47" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="48" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="49" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="50" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="51" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="52" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="53" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="54" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="55" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="56" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="57" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="58" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="59" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
+        <f t="shared" ref="O45:O46" si="3">IF(AND(I45="",N45=""),"",IF(AND(I45="",ISNUMBER(N45)),N45,IF(AND(N45="",ISNUMBER(I45)),I45,IF(AND(ISNUMBER(I45),ISNUMBER(N45)),I45+N45,""))))</f>
+        <v>0</v>
+      </c>
+      <c r="P45" s="18"/>
+      <c r="Q45" s="19"/>
+      <c r="R45" s="20"/>
+    </row>
+    <row r="46" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="10">
+        <v>37</v>
+      </c>
+      <c r="B46" s="2"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="11"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+      <c r="M46" s="11"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="12">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P46" s="18"/>
+      <c r="Q46" s="19"/>
+      <c r="R46" s="20"/>
+    </row>
+    <row r="47" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="10">
+        <v>38</v>
+      </c>
+      <c r="B47" s="2"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="12">
+        <f t="shared" ref="I47:I81" si="4">SUM(E47:H47)</f>
+        <v>0</v>
+      </c>
+      <c r="J47" s="11"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="11"/>
+      <c r="M47" s="11"/>
+      <c r="N47" s="10"/>
+      <c r="O47" s="12">
+        <f t="shared" ref="O47:O81" si="5">IF(AND(I47="",N47=""),"",IF(AND(I47="",ISNUMBER(N47)),N47,IF(AND(N47="",ISNUMBER(I47)),I47,IF(AND(ISNUMBER(I47),ISNUMBER(N47)),I47+N47,""))))</f>
+        <v>0</v>
+      </c>
+      <c r="P47" s="18"/>
+      <c r="Q47" s="19"/>
+      <c r="R47" s="20"/>
+    </row>
+    <row r="48" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="10">
+        <v>39</v>
+      </c>
+      <c r="B48" s="2"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J48" s="11"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="11"/>
+      <c r="M48" s="11"/>
+      <c r="N48" s="10"/>
+      <c r="O48" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P48" s="18"/>
+      <c r="Q48" s="19"/>
+      <c r="R48" s="20"/>
+    </row>
+    <row r="49" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="10">
+        <v>40</v>
+      </c>
+      <c r="B49" s="2"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J49" s="11"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="11"/>
+      <c r="M49" s="11"/>
+      <c r="N49" s="10"/>
+      <c r="O49" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P49" s="18"/>
+      <c r="Q49" s="19"/>
+      <c r="R49" s="20"/>
+    </row>
+    <row r="50" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="10">
+        <v>41</v>
+      </c>
+      <c r="B50" s="2"/>
+      <c r="C50" s="15"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="11"/>
+      <c r="K50" s="11"/>
+      <c r="L50" s="11"/>
+      <c r="M50" s="11"/>
+      <c r="N50" s="10"/>
+      <c r="O50" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P50" s="18"/>
+      <c r="Q50" s="19"/>
+      <c r="R50" s="20"/>
+    </row>
+    <row r="51" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="10">
+        <v>42</v>
+      </c>
+      <c r="B51" s="2"/>
+      <c r="C51" s="15"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="11"/>
+      <c r="K51" s="11"/>
+      <c r="L51" s="11"/>
+      <c r="M51" s="11"/>
+      <c r="N51" s="10"/>
+      <c r="O51" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P51" s="18"/>
+      <c r="Q51" s="19"/>
+      <c r="R51" s="20"/>
+    </row>
+    <row r="52" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A52" s="10">
+        <v>43</v>
+      </c>
+      <c r="B52" s="2"/>
+      <c r="C52" s="15"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="11"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J52" s="11"/>
+      <c r="K52" s="11"/>
+      <c r="L52" s="11"/>
+      <c r="M52" s="11"/>
+      <c r="N52" s="10"/>
+      <c r="O52" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P52" s="18"/>
+      <c r="Q52" s="19"/>
+      <c r="R52" s="20"/>
+    </row>
+    <row r="53" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="10">
+        <v>44</v>
+      </c>
+      <c r="B53" s="2"/>
+      <c r="C53" s="15"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="11"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="11"/>
+      <c r="K53" s="11"/>
+      <c r="L53" s="11"/>
+      <c r="M53" s="11"/>
+      <c r="N53" s="10"/>
+      <c r="O53" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P53" s="18"/>
+      <c r="Q53" s="19"/>
+      <c r="R53" s="20"/>
+    </row>
+    <row r="54" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A54" s="10">
+        <v>45</v>
+      </c>
+      <c r="B54" s="2"/>
+      <c r="C54" s="15"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="11"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="11"/>
+      <c r="H54" s="11"/>
+      <c r="I54" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J54" s="11"/>
+      <c r="K54" s="11"/>
+      <c r="L54" s="11"/>
+      <c r="M54" s="11"/>
+      <c r="N54" s="10"/>
+      <c r="O54" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P54" s="18"/>
+      <c r="Q54" s="19"/>
+      <c r="R54" s="20"/>
+    </row>
+    <row r="55" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A55" s="10">
+        <v>46</v>
+      </c>
+      <c r="B55" s="2"/>
+      <c r="C55" s="15"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="11"/>
+      <c r="F55" s="11"/>
+      <c r="G55" s="11"/>
+      <c r="H55" s="11"/>
+      <c r="I55" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="11"/>
+      <c r="K55" s="11"/>
+      <c r="L55" s="11"/>
+      <c r="M55" s="11"/>
+      <c r="N55" s="10"/>
+      <c r="O55" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P55" s="18"/>
+      <c r="Q55" s="19"/>
+      <c r="R55" s="20"/>
+    </row>
+    <row r="56" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A56" s="10">
+        <v>47</v>
+      </c>
+      <c r="B56" s="2"/>
+      <c r="C56" s="15"/>
+      <c r="D56" s="15"/>
+      <c r="E56" s="11"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="11"/>
+      <c r="H56" s="11"/>
+      <c r="I56" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="11"/>
+      <c r="K56" s="11"/>
+      <c r="L56" s="11"/>
+      <c r="M56" s="11"/>
+      <c r="N56" s="10"/>
+      <c r="O56" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P56" s="18"/>
+      <c r="Q56" s="19"/>
+      <c r="R56" s="20"/>
+    </row>
+    <row r="57" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A57" s="10">
+        <v>48</v>
+      </c>
+      <c r="B57" s="2"/>
+      <c r="C57" s="15"/>
+      <c r="D57" s="15"/>
+      <c r="E57" s="11"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11"/>
+      <c r="H57" s="11"/>
+      <c r="I57" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="11"/>
+      <c r="K57" s="11"/>
+      <c r="L57" s="11"/>
+      <c r="M57" s="11"/>
+      <c r="N57" s="10"/>
+      <c r="O57" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P57" s="18"/>
+      <c r="Q57" s="19"/>
+      <c r="R57" s="20"/>
+    </row>
+    <row r="58" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A58" s="10">
+        <v>49</v>
+      </c>
+      <c r="B58" s="2"/>
+      <c r="C58" s="15"/>
+      <c r="D58" s="15"/>
+      <c r="E58" s="11"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="11"/>
+      <c r="I58" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="11"/>
+      <c r="K58" s="11"/>
+      <c r="L58" s="11"/>
+      <c r="M58" s="11"/>
+      <c r="N58" s="10"/>
+      <c r="O58" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P58" s="18"/>
+      <c r="Q58" s="19"/>
+      <c r="R58" s="20"/>
+    </row>
+    <row r="59" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A59" s="10">
+        <v>50</v>
+      </c>
+      <c r="B59" s="2"/>
+      <c r="C59" s="15"/>
+      <c r="D59" s="15"/>
+      <c r="E59" s="11"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="11"/>
+      <c r="I59" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="11"/>
+      <c r="K59" s="11"/>
+      <c r="L59" s="11"/>
+      <c r="M59" s="11"/>
+      <c r="N59" s="10"/>
+      <c r="O59" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P59" s="18"/>
+      <c r="Q59" s="19"/>
+      <c r="R59" s="20"/>
+    </row>
+    <row r="60" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A60" s="10">
+        <v>51</v>
+      </c>
+      <c r="B60" s="2"/>
+      <c r="C60" s="15"/>
+      <c r="D60" s="15"/>
+      <c r="E60" s="11"/>
+      <c r="F60" s="11"/>
+      <c r="G60" s="11"/>
+      <c r="H60" s="11"/>
+      <c r="I60" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J60" s="11"/>
+      <c r="K60" s="11"/>
+      <c r="L60" s="11"/>
+      <c r="M60" s="11"/>
+      <c r="N60" s="10"/>
+      <c r="O60" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P60" s="18"/>
+      <c r="Q60" s="19"/>
+      <c r="R60" s="20"/>
+    </row>
+    <row r="61" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A61" s="10">
+        <v>52</v>
+      </c>
+      <c r="B61" s="2"/>
+      <c r="C61" s="15"/>
+      <c r="D61" s="15"/>
+      <c r="E61" s="11"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="11"/>
+      <c r="I61" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J61" s="11"/>
+      <c r="K61" s="11"/>
+      <c r="L61" s="11"/>
+      <c r="M61" s="11"/>
+      <c r="N61" s="10"/>
+      <c r="O61" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P61" s="18"/>
+      <c r="Q61" s="19"/>
+      <c r="R61" s="20"/>
+    </row>
+    <row r="62" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A62" s="10">
+        <v>53</v>
+      </c>
+      <c r="B62" s="2"/>
+      <c r="C62" s="15"/>
+      <c r="D62" s="15"/>
+      <c r="E62" s="11"/>
+      <c r="F62" s="11"/>
+      <c r="G62" s="11"/>
+      <c r="H62" s="11"/>
+      <c r="I62" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J62" s="11"/>
+      <c r="K62" s="11"/>
+      <c r="L62" s="11"/>
+      <c r="M62" s="11"/>
+      <c r="N62" s="10"/>
+      <c r="O62" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P62" s="18"/>
+      <c r="Q62" s="19"/>
+      <c r="R62" s="20"/>
+    </row>
+    <row r="63" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A63" s="10">
+        <v>54</v>
+      </c>
+      <c r="B63" s="2"/>
+      <c r="C63" s="15"/>
+      <c r="D63" s="15"/>
+      <c r="E63" s="11"/>
+      <c r="F63" s="11"/>
+      <c r="G63" s="11"/>
+      <c r="H63" s="11"/>
+      <c r="I63" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J63" s="11"/>
+      <c r="K63" s="11"/>
+      <c r="L63" s="11"/>
+      <c r="M63" s="11"/>
+      <c r="N63" s="10"/>
+      <c r="O63" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P63" s="18"/>
+      <c r="Q63" s="19"/>
+      <c r="R63" s="20"/>
+    </row>
+    <row r="64" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A64" s="10">
+        <v>55</v>
+      </c>
+      <c r="B64" s="2"/>
+      <c r="C64" s="15"/>
+      <c r="D64" s="15"/>
+      <c r="E64" s="11"/>
+      <c r="F64" s="11"/>
+      <c r="G64" s="11"/>
+      <c r="H64" s="11"/>
+      <c r="I64" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J64" s="11"/>
+      <c r="K64" s="11"/>
+      <c r="L64" s="11"/>
+      <c r="M64" s="11"/>
+      <c r="N64" s="10"/>
+      <c r="O64" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P64" s="18"/>
+      <c r="Q64" s="19"/>
+      <c r="R64" s="20"/>
+    </row>
+    <row r="65" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A65" s="10">
+        <v>56</v>
+      </c>
+      <c r="B65" s="2"/>
+      <c r="C65" s="15"/>
+      <c r="D65" s="15"/>
+      <c r="E65" s="11"/>
+      <c r="F65" s="11"/>
+      <c r="G65" s="11"/>
+      <c r="H65" s="11"/>
+      <c r="I65" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J65" s="11"/>
+      <c r="K65" s="11"/>
+      <c r="L65" s="11"/>
+      <c r="M65" s="11"/>
+      <c r="N65" s="10"/>
+      <c r="O65" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P65" s="18"/>
+      <c r="Q65" s="19"/>
+      <c r="R65" s="20"/>
+    </row>
+    <row r="66" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A66" s="10">
+        <v>57</v>
+      </c>
+      <c r="B66" s="2"/>
+      <c r="C66" s="15"/>
+      <c r="D66" s="15"/>
+      <c r="E66" s="11"/>
+      <c r="F66" s="11"/>
+      <c r="G66" s="11"/>
+      <c r="H66" s="11"/>
+      <c r="I66" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J66" s="11"/>
+      <c r="K66" s="11"/>
+      <c r="L66" s="11"/>
+      <c r="M66" s="11"/>
+      <c r="N66" s="10"/>
+      <c r="O66" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P66" s="18"/>
+      <c r="Q66" s="19"/>
+      <c r="R66" s="20"/>
+    </row>
+    <row r="67" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A67" s="10">
+        <v>58</v>
+      </c>
+      <c r="B67" s="2"/>
+      <c r="C67" s="15"/>
+      <c r="D67" s="15"/>
+      <c r="E67" s="11"/>
+      <c r="F67" s="11"/>
+      <c r="G67" s="11"/>
+      <c r="H67" s="11"/>
+      <c r="I67" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J67" s="11"/>
+      <c r="K67" s="11"/>
+      <c r="L67" s="11"/>
+      <c r="M67" s="11"/>
+      <c r="N67" s="10"/>
+      <c r="O67" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P67" s="18"/>
+      <c r="Q67" s="19"/>
+      <c r="R67" s="20"/>
+    </row>
+    <row r="68" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A68" s="10">
+        <v>59</v>
+      </c>
+      <c r="B68" s="2"/>
+      <c r="C68" s="15"/>
+      <c r="D68" s="15"/>
+      <c r="E68" s="11"/>
+      <c r="F68" s="11"/>
+      <c r="G68" s="11"/>
+      <c r="H68" s="11"/>
+      <c r="I68" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J68" s="11"/>
+      <c r="K68" s="11"/>
+      <c r="L68" s="11"/>
+      <c r="M68" s="11"/>
+      <c r="N68" s="10"/>
+      <c r="O68" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P68" s="18"/>
+      <c r="Q68" s="19"/>
+      <c r="R68" s="20"/>
+    </row>
+    <row r="69" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A69" s="10">
+        <v>60</v>
+      </c>
+      <c r="B69" s="2"/>
+      <c r="C69" s="15"/>
+      <c r="D69" s="15"/>
+      <c r="E69" s="11"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="11"/>
+      <c r="I69" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J69" s="11"/>
+      <c r="K69" s="11"/>
+      <c r="L69" s="11"/>
+      <c r="M69" s="11"/>
+      <c r="N69" s="10"/>
+      <c r="O69" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P69" s="18"/>
+      <c r="Q69" s="19"/>
+      <c r="R69" s="20"/>
+    </row>
+    <row r="70" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A70" s="10">
+        <v>61</v>
+      </c>
+      <c r="B70" s="2"/>
+      <c r="C70" s="15"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="11"/>
+      <c r="G70" s="11"/>
+      <c r="H70" s="11"/>
+      <c r="I70" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J70" s="11"/>
+      <c r="K70" s="11"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="10"/>
+      <c r="O70" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P70" s="18"/>
+      <c r="Q70" s="19"/>
+      <c r="R70" s="20"/>
+    </row>
+    <row r="71" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A71" s="10">
+        <v>62</v>
+      </c>
+      <c r="B71" s="2"/>
+      <c r="C71" s="15"/>
+      <c r="D71" s="15"/>
+      <c r="E71" s="11"/>
+      <c r="F71" s="11"/>
+      <c r="G71" s="11"/>
+      <c r="H71" s="11"/>
+      <c r="I71" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J71" s="11"/>
+      <c r="K71" s="11"/>
+      <c r="L71" s="11"/>
+      <c r="M71" s="11"/>
+      <c r="N71" s="10"/>
+      <c r="O71" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P71" s="18"/>
+      <c r="Q71" s="19"/>
+      <c r="R71" s="20"/>
+    </row>
+    <row r="72" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A72" s="10">
+        <v>63</v>
+      </c>
+      <c r="B72" s="2"/>
+      <c r="C72" s="15"/>
+      <c r="D72" s="15"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="11"/>
+      <c r="I72" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J72" s="11"/>
+      <c r="K72" s="11"/>
+      <c r="L72" s="11"/>
+      <c r="M72" s="11"/>
+      <c r="N72" s="10"/>
+      <c r="O72" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P72" s="18"/>
+      <c r="Q72" s="19"/>
+      <c r="R72" s="20"/>
+    </row>
+    <row r="73" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A73" s="10">
+        <v>64</v>
+      </c>
+      <c r="B73" s="2"/>
+      <c r="C73" s="15"/>
+      <c r="D73" s="15"/>
+      <c r="E73" s="11"/>
+      <c r="F73" s="11"/>
+      <c r="G73" s="11"/>
+      <c r="H73" s="11"/>
+      <c r="I73" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J73" s="11"/>
+      <c r="K73" s="11"/>
+      <c r="L73" s="11"/>
+      <c r="M73" s="11"/>
+      <c r="N73" s="10"/>
+      <c r="O73" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P73" s="18"/>
+      <c r="Q73" s="19"/>
+      <c r="R73" s="20"/>
+    </row>
+    <row r="74" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A74" s="10">
+        <v>65</v>
+      </c>
+      <c r="B74" s="2"/>
+      <c r="C74" s="15"/>
+      <c r="D74" s="15"/>
+      <c r="E74" s="11"/>
+      <c r="F74" s="11"/>
+      <c r="G74" s="11"/>
+      <c r="H74" s="11"/>
+      <c r="I74" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J74" s="11"/>
+      <c r="K74" s="11"/>
+      <c r="L74" s="11"/>
+      <c r="M74" s="11"/>
+      <c r="N74" s="10"/>
+      <c r="O74" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P74" s="18"/>
+      <c r="Q74" s="19"/>
+      <c r="R74" s="20"/>
+    </row>
+    <row r="75" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A75" s="10">
+        <v>66</v>
+      </c>
+      <c r="B75" s="2"/>
+      <c r="C75" s="15"/>
+      <c r="D75" s="15"/>
+      <c r="E75" s="11"/>
+      <c r="F75" s="11"/>
+      <c r="G75" s="11"/>
+      <c r="H75" s="11"/>
+      <c r="I75" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J75" s="11"/>
+      <c r="K75" s="11"/>
+      <c r="L75" s="11"/>
+      <c r="M75" s="11"/>
+      <c r="N75" s="10"/>
+      <c r="O75" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P75" s="18"/>
+      <c r="Q75" s="19"/>
+      <c r="R75" s="20"/>
+    </row>
+    <row r="76" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A76" s="10">
+        <v>67</v>
+      </c>
+      <c r="B76" s="2"/>
+      <c r="C76" s="15"/>
+      <c r="D76" s="15"/>
+      <c r="E76" s="11"/>
+      <c r="F76" s="11"/>
+      <c r="G76" s="11"/>
+      <c r="H76" s="11"/>
+      <c r="I76" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J76" s="11"/>
+      <c r="K76" s="11"/>
+      <c r="L76" s="11"/>
+      <c r="M76" s="11"/>
+      <c r="N76" s="10"/>
+      <c r="O76" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P76" s="18"/>
+      <c r="Q76" s="19"/>
+      <c r="R76" s="20"/>
+    </row>
+    <row r="77" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A77" s="10">
+        <v>68</v>
+      </c>
+      <c r="B77" s="2"/>
+      <c r="C77" s="15"/>
+      <c r="D77" s="15"/>
+      <c r="E77" s="11"/>
+      <c r="F77" s="11"/>
+      <c r="G77" s="11"/>
+      <c r="H77" s="11"/>
+      <c r="I77" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J77" s="11"/>
+      <c r="K77" s="11"/>
+      <c r="L77" s="11"/>
+      <c r="M77" s="11"/>
+      <c r="N77" s="10"/>
+      <c r="O77" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P77" s="18"/>
+      <c r="Q77" s="19"/>
+      <c r="R77" s="20"/>
+    </row>
+    <row r="78" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A78" s="10">
+        <v>69</v>
+      </c>
+      <c r="B78" s="2"/>
+      <c r="C78" s="15"/>
+      <c r="D78" s="15"/>
+      <c r="E78" s="11"/>
+      <c r="F78" s="11"/>
+      <c r="G78" s="11"/>
+      <c r="H78" s="11"/>
+      <c r="I78" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J78" s="11"/>
+      <c r="K78" s="11"/>
+      <c r="L78" s="11"/>
+      <c r="M78" s="11"/>
+      <c r="N78" s="10"/>
+      <c r="O78" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P78" s="18"/>
+      <c r="Q78" s="19"/>
+      <c r="R78" s="20"/>
+    </row>
+    <row r="79" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A79" s="10">
+        <v>70</v>
+      </c>
+      <c r="B79" s="2"/>
+      <c r="C79" s="15"/>
+      <c r="D79" s="15"/>
+      <c r="E79" s="11"/>
+      <c r="F79" s="11"/>
+      <c r="G79" s="11"/>
+      <c r="H79" s="11"/>
+      <c r="I79" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J79" s="11"/>
+      <c r="K79" s="11"/>
+      <c r="L79" s="11"/>
+      <c r="M79" s="11"/>
+      <c r="N79" s="10"/>
+      <c r="O79" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P79" s="18"/>
+      <c r="Q79" s="19"/>
+      <c r="R79" s="20"/>
+    </row>
+    <row r="80" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A80" s="10">
+        <v>71</v>
+      </c>
+      <c r="B80" s="2"/>
+      <c r="C80" s="15"/>
+      <c r="D80" s="15"/>
+      <c r="E80" s="11"/>
+      <c r="F80" s="11"/>
+      <c r="G80" s="11"/>
+      <c r="H80" s="11"/>
+      <c r="I80" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J80" s="11"/>
+      <c r="K80" s="11"/>
+      <c r="L80" s="11"/>
+      <c r="M80" s="11"/>
+      <c r="N80" s="10"/>
+      <c r="O80" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P80" s="18"/>
+      <c r="Q80" s="19"/>
+      <c r="R80" s="20"/>
+    </row>
+    <row r="81" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A81" s="10">
+        <v>72</v>
+      </c>
+      <c r="B81" s="2"/>
+      <c r="C81" s="15"/>
+      <c r="D81" s="15"/>
+      <c r="E81" s="11"/>
+      <c r="F81" s="11"/>
+      <c r="G81" s="11"/>
+      <c r="H81" s="11"/>
+      <c r="I81" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J81" s="11"/>
+      <c r="K81" s="11"/>
+      <c r="L81" s="11"/>
+      <c r="M81" s="11"/>
+      <c r="N81" s="10"/>
+      <c r="O81" s="12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P81" s="18"/>
+      <c r="Q81" s="19"/>
+      <c r="R81" s="20"/>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C21:H22">
     <sortCondition ref="C21"/>
   </sortState>
-  <mergeCells count="69">
-    <mergeCell ref="P45:R45"/>
-    <mergeCell ref="P44:R44"/>
-    <mergeCell ref="P11:R11"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="O6:Q6"/>
-    <mergeCell ref="P8:R8"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="O7:Q7"/>
+  <mergeCells count="105">
+    <mergeCell ref="P77:R77"/>
+    <mergeCell ref="P78:R78"/>
+    <mergeCell ref="P79:R79"/>
+    <mergeCell ref="P80:R80"/>
+    <mergeCell ref="P81:R81"/>
+    <mergeCell ref="P72:R72"/>
+    <mergeCell ref="P73:R73"/>
+    <mergeCell ref="P74:R74"/>
+    <mergeCell ref="P75:R75"/>
+    <mergeCell ref="P76:R76"/>
+    <mergeCell ref="P67:R67"/>
+    <mergeCell ref="P68:R68"/>
+    <mergeCell ref="P69:R69"/>
+    <mergeCell ref="P70:R70"/>
+    <mergeCell ref="P71:R71"/>
+    <mergeCell ref="P62:R62"/>
+    <mergeCell ref="P63:R63"/>
+    <mergeCell ref="P64:R64"/>
+    <mergeCell ref="P65:R65"/>
+    <mergeCell ref="P66:R66"/>
+    <mergeCell ref="P57:R57"/>
+    <mergeCell ref="P58:R58"/>
+    <mergeCell ref="P59:R59"/>
+    <mergeCell ref="P60:R60"/>
+    <mergeCell ref="P61:R61"/>
+    <mergeCell ref="P52:R52"/>
+    <mergeCell ref="P53:R53"/>
+    <mergeCell ref="P54:R54"/>
+    <mergeCell ref="P55:R55"/>
+    <mergeCell ref="P56:R56"/>
+    <mergeCell ref="P47:R47"/>
+    <mergeCell ref="P48:R48"/>
+    <mergeCell ref="P49:R49"/>
+    <mergeCell ref="P50:R50"/>
+    <mergeCell ref="P51:R51"/>
+    <mergeCell ref="P33:R33"/>
+    <mergeCell ref="P34:R34"/>
+    <mergeCell ref="P35:R35"/>
+    <mergeCell ref="P36:R36"/>
+    <mergeCell ref="P46:R46"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="P23:R23"/>
+    <mergeCell ref="P24:R24"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="L8:O8"/>
+    <mergeCell ref="P19:R19"/>
+    <mergeCell ref="P20:R20"/>
+    <mergeCell ref="P21:R21"/>
+    <mergeCell ref="P22:R22"/>
+    <mergeCell ref="P16:R16"/>
+    <mergeCell ref="P17:R17"/>
+    <mergeCell ref="P18:R18"/>
+    <mergeCell ref="O5:Q5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="P43:R43"/>
+    <mergeCell ref="P9:R9"/>
+    <mergeCell ref="P38:R38"/>
+    <mergeCell ref="P39:R39"/>
+    <mergeCell ref="P40:R40"/>
+    <mergeCell ref="P41:R41"/>
+    <mergeCell ref="P42:R42"/>
+    <mergeCell ref="P10:R10"/>
+    <mergeCell ref="P13:R13"/>
+    <mergeCell ref="P12:R12"/>
+    <mergeCell ref="P14:R14"/>
+    <mergeCell ref="P15:R15"/>
+    <mergeCell ref="P25:R25"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="F8:H8"/>
@@ -2734,46 +3766,27 @@
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="L5:N5"/>
-    <mergeCell ref="O5:Q5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="P43:R43"/>
-    <mergeCell ref="P9:R9"/>
-    <mergeCell ref="P38:R38"/>
-    <mergeCell ref="P39:R39"/>
-    <mergeCell ref="P40:R40"/>
-    <mergeCell ref="P41:R41"/>
-    <mergeCell ref="P42:R42"/>
-    <mergeCell ref="P10:R10"/>
-    <mergeCell ref="P13:R13"/>
-    <mergeCell ref="P12:R12"/>
-    <mergeCell ref="P14:R14"/>
-    <mergeCell ref="P15:R15"/>
-    <mergeCell ref="P25:R25"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="P45:R45"/>
+    <mergeCell ref="P44:R44"/>
+    <mergeCell ref="P11:R11"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="P8:R8"/>
+    <mergeCell ref="O7:Q7"/>
     <mergeCell ref="P26:R26"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="P23:R23"/>
-    <mergeCell ref="P24:R24"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="L8:O8"/>
     <mergeCell ref="P27:R27"/>
-    <mergeCell ref="P19:R19"/>
-    <mergeCell ref="P20:R20"/>
-    <mergeCell ref="P21:R21"/>
-    <mergeCell ref="P22:R22"/>
-    <mergeCell ref="P16:R16"/>
-    <mergeCell ref="P17:R17"/>
-    <mergeCell ref="P18:R18"/>
     <mergeCell ref="P28:R28"/>
     <mergeCell ref="P29:R29"/>
     <mergeCell ref="P30:R30"/>
     <mergeCell ref="P31:R31"/>
     <mergeCell ref="P37:R37"/>
     <mergeCell ref="P32:R32"/>
-    <mergeCell ref="P33:R33"/>
-    <mergeCell ref="P34:R34"/>
-    <mergeCell ref="P35:R35"/>
-    <mergeCell ref="P36:R36"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations disablePrompts="1" count="2">
@@ -2790,6 +3803,9 @@
     <oddHeader>&amp;R&amp;"-,太字"&amp;12⑫</oddHeader>
     <oddFooter>&amp;C一般社団法人　日本クレー射撃協会</oddFooter>
   </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="45" max="16383" man="1"/>
+  </rowBreaks>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>